--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T09:58:03+00:00</t>
+    <t>2026-01-26T12:56:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T12:56:49+00:00</t>
+    <t>2026-02-05T13:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Goal|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Goal</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -623,7 +623,7 @@
     <t>referenceEvaluation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-evaluation-reference|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-evaluation-reference}
 </t>
   </si>
   <si>
@@ -646,7 +646,7 @@
     <t>referenceProjetPerso</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-careplan-reference|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-careplan-reference}
 </t>
   </si>
   <si>
@@ -665,7 +665,7 @@
     <t>pieceJointeObjectif</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment}
 </t>
   </si>
   <si>
@@ -938,7 +938,7 @@
     <t>auteurStatut</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-status-author|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-status-author}
 </t>
   </si>
   <si>
@@ -1121,7 +1121,7 @@
     <t>Goal.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins)
 </t>
   </si>
   <si>
@@ -1336,7 +1336,7 @@
     <t>Goal.expressedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner)
 </t>
   </si>
   <si>
@@ -1358,7 +1358,7 @@
     <t>Goal.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-service-request-besoin|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-service-request-besoin)
 </t>
   </si>
   <si>
@@ -1424,7 +1424,7 @@
     <t>3</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-discriminator|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-discriminator}
 </t>
   </si>
   <si>
@@ -1565,7 +1565,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-goal-objectif-note-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-goal-objectif-note-vs</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -2020,7 +2020,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="158.5546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="139.5390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2035,7 +2035,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="131.83984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.63671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="86.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T13:38:35+00:00</t>
+    <t>2026-02-05T14:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T14:50:20+00:00</t>
+    <t>2026-02-05T15:15:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -627,7 +627,7 @@
 </t>
   </si>
   <si>
-    <t>Lien vers l'évaluation</t>
+    <t>TDDUI Evaluation Ref</t>
   </si>
   <si>
     <t>Liens vers l'évaluation, utilisables dans le profil TDDUIGoalObjectif.</t>
@@ -650,7 +650,7 @@
 </t>
   </si>
   <si>
-    <t>Lien vers le projet personnalisé</t>
+    <t>TDDUI CarePlan Projet Perso Ref</t>
   </si>
   <si>
     <t>Liens vers le projet personnalisé, utilisables dans le profil TDDUIGoalObjectif.</t>
@@ -669,7 +669,7 @@
 </t>
   </si>
   <si>
-    <t>Pièce jointe</t>
+    <t>TDDUI Attachment</t>
   </si>
   <si>
     <t>Extension permettant de véhiculer des pièces jointes que ce soit pour l'évaluation, l'évènement ou le projet personnalisé. L'extension référence le profil PDSm_SimplifiedPublish.</t>
@@ -942,7 +942,7 @@
 </t>
   </si>
   <si>
-    <t>TDDUI Auteur statut</t>
+    <t>TDDUI Status Author</t>
   </si>
   <si>
     <t>Extension permettant de représenter la profession du professionnel.</t>
@@ -1428,7 +1428,7 @@
 </t>
   </si>
   <si>
-    <t>TDDUI Discriminator Extension</t>
+    <t>TDDUI Discriminator</t>
   </si>
   <si>
     <t>Extension pour discriminer les éléments CarePlan.supportingInfo et Goal.note.</t>
@@ -1559,13 +1559,13 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="titreObjectif"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-goal-objectif-note-vs</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-goal-objectif-note</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1612,7 +1612,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="avisUsagerObjectif"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1659,7 +1659,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="strategieMiseEnOeuvreObjectif"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -2035,7 +2035,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="131.83984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.63671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.3203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="86.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T15:15:02+00:00</t>
+    <t>2026-02-06T13:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T13:40:54+00:00</t>
+    <t>2026-02-06T14:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T15:19:47+00:00</t>
+    <t>2026-02-25T14:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T14:12:38+00:00</t>
+    <t>2026-02-26T10:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -945,7 +945,7 @@
     <t>TDDUI Status Author</t>
   </si>
   <si>
-    <t>Extension permettant de représenter la profession du professionnel.</t>
+    <t>Extension permettant de représenter l'auteur du statut.</t>
   </si>
   <si>
     <t>statutObjectif.auteur</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:50:19+00:00</t>
+    <t>2026-02-26T16:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:06:51+00:00</t>
+    <t>2026-02-27T10:48:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:48:32+00:00</t>
+    <t>2026-02-27T17:34:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T17:34:14+00:00</t>
+    <t>2026-03-02T09:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T09:04:22+00:00</t>
+    <t>2026-03-02T10:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T10:45:03+00:00</t>
+    <t>2026-03-02T11:00:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T11:00:56+00:00</t>
+    <t>2026-03-16T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:16:38+00:00</t>
+    <t>2026-03-16T15:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:31:45+00:00</t>
+    <t>2026-03-17T17:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T17:41:27+00:00</t>
+    <t>2026-04-09T09:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:33:58+00:00</t>
+    <t>2026-05-07T09:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T09:37:23+00:00</t>
+    <t>2026-06-10T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T13:07:20+00:00</t>
+    <t>2026-06-16T08:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:06:32+00:00</t>
+    <t>2026-06-16T08:52:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:52:34+00:00</t>
+    <t>2026-06-16T09:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T09:33:33+00:00</t>
+    <t>2026-06-16T10:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:35:13+00:00</t>
+    <t>2026-06-16T10:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:46:14+00:00</t>
+    <t>2026-06-16T11:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T11:08:56+00:00</t>
+    <t>2026-06-16T14:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:39:41+00:00</t>
+    <t>2026-06-16T16:50:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:50:35+00:00</t>
+    <t>2026-06-17T09:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:02:27+00:00</t>
+    <t>2026-06-17T09:20:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:20:14+00:00</t>
+    <t>2026-06-29T13:11:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:11:00+00:00</t>
+    <t>2026-06-30T08:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:27:53+00:00</t>
+    <t>2026-06-30T13:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:41:45+00:00</t>
+    <t>2026-06-30T14:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:01:12+00:00</t>
+    <t>2026-06-30T14:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:55:37+00:00</t>
+    <t>2026-07-01T09:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T09:47:49+00:00</t>
+    <t>2026-07-01T11:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:47:31+00:00</t>
+    <t>2026-07-01T13:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:17:54+00:00</t>
+    <t>2026-07-01T14:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:33:44+00:00</t>
+    <t>2026-07-01T14:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:55:22+00:00</t>
+    <t>2026-07-01T15:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:33:30+00:00</t>
+    <t>2026-07-20T07:42:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.4.0-ballot</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:42:46+00:00</t>
+    <t>2026-07-22T13:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/main/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:04:03+00:00</t>
+    <t>2026-07-22T14:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
